--- a/Template_Skrining.xlsx
+++ b/Template_Skrining.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lihan\AUTOMATION\BPJS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5FBE9487-B884-4921-97EE-25E0EC930EF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2F689C0-1FE4-4B5F-81FE-27399468CCA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HASIL" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>NAMA</t>
   </si>
@@ -31,9 +31,6 @@
     <t>JENIK_KELAMIN</t>
   </si>
   <si>
-    <t>TEMPAT</t>
-  </si>
-  <si>
     <t>TGL_LAHIR</t>
   </si>
   <si>
@@ -65,13 +62,19 @@
   </si>
   <si>
     <t>opsional, bisa di isi sesuai data atau dikosongi nanti otomatis</t>
+  </si>
+  <si>
+    <t>65656565656565</t>
+  </si>
+  <si>
+    <t>TINGGAL TARIK KEBAWAH, LANGSUNG KEISI OTOMATIS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -79,8 +82,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -105,6 +115,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC189F7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -118,12 +134,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -463,35 +484,36 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="3" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>4</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="2" t="s">
@@ -503,32 +525,46 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="5" t="str">
+        <f t="shared" ref="C2" ca="1" si="0">TEXT(DATE(IF(VALUE(MID(A2,11,2))&lt;=VALUE(RIGHT(YEAR(TODAY()), 2)), 2000+VALUE(MID(A2,11,2)), 1900+VALUE(MID(A2,11,2))), VALUE(MID(A2,9,2)), IF(VALUE(MID(A2,7,2))&gt;40, VALUE(MID(A2,7,2))-40, VALUE(MID(A2,7,2)))), "dd-mm-yyyy")</f>
+        <v>25-05-1970</v>
+      </c>
+      <c r="D2" s="6" t="str">
+        <f t="shared" ref="D2" si="1">IF(A2&lt;&gt;"",IF(VALUE(MID(A2,7,2))&gt;40,"Perempuan","Laki-laki"),"")</f>
+        <v>Perempuan</v>
+      </c>
+      <c r="N2" s="2"/>
+      <c r="O2" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="O2" s="2"/>
-      <c r="P2" s="1" t="s">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N3" s="3"/>
+      <c r="O3" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="O3" s="3"/>
-      <c r="P3" s="1" t="s">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N4" s="4"/>
+      <c r="O4" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="O4" s="4"/>
-      <c r="P4" s="1" t="s">
-        <v>14</v>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N5" s="7"/>
+      <c r="O5" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="D1:E1 A1:B1 F1:L1" numberStoredAsText="1"/>
+    <ignoredError sqref="D1 E1:K1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>